--- a/cache/open_items_2026-05-31.xlsx
+++ b/cache/open_items_2026-05-31.xlsx
@@ -752,13 +752,13 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="75" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PICK-FORENSICS</t>
+          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Audit / Attribution</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
+          <t>Weekend phantom picks in audit ledger</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
+          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>scripts/pick_forensics.py + dashboard tab</t>
+          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -798,13 +798,13 @@
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
     </row>
-    <row r="4" ht="75" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>BUG-WEEKEND-PHANTOM-PICKS</t>
+          <t>DATA-BROKEN-IPO-CALENDAR</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -814,22 +814,22 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Data / Calendars (broken)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Weekend phantom picks in audit ledger</t>
+          <t>ipo_calendar — NASDAQ API times out</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Audit ledger shows phantom picks on May 10 (Sun), May 16 (Sat), May 17 (Sun) — markets closed. Likely a scan-date assignment bug (writing today's date to a Friday pick that re-scans on Sat/Sun, or weekend cron runs that should skip).</t>
+          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Trace which writer emits these entries: check run_daily_scan.sh weekday gate, swing_trade.py scan-date logic, and infra/prototype/build_audit_ledger.py date assignment. Weekend launchd should be gated; if it runs intentionally for paper-resolve, mark those rows as REPLAY not PICK.</t>
+          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-IPO-CALENDAR</t>
+          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (broken)</t>
+          <t>Data / Catalysts (broken)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>ipo_calendar — NASDAQ API times out</t>
+          <t>congressional_trades — sources dead</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>NASDAQ public IPO API times out from this host (~30s no response). Calendar slot is wired but produces 0 rows.</t>
+          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Investigate timeout first (UA headers / proxy / rate-limited IP) before alt-source. Candidate alternates: SEC S-1 filings via EDGAR full-text-search, IPO Monitor RSS, Yahoo Finance IPO page.</t>
+          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DATA-BROKEN-CONGRESSIONAL-TRADES</t>
+          <t>PARITY-REALTIME-DATA</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -906,22 +906,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Data / Catalysts (broken)</t>
+          <t>Data / Infrastructure / Platform Parity</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades — sources dead</t>
+          <t>Real-Time Data (streaming quotes)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Senate Stock Watcher GitHub + S3 mirror both return dead/empty responses. The catalysts slot is wired but the scraper produces 0 rows.</t>
+          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Replace dead source with direct efts.sec.gov integration (Form 4 XBRL parsing); add House Clerk site fallback for House STOCK Act filings. Scope: 1-2d dev + XBRL schema work. Free-data only per CLAUDE.md.</t>
+          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -936,13 +936,13 @@
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>PARITY-REALTIME-DATA</t>
+          <t>MODE-4</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Data / Infrastructure / Platform Parity</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Data (streaming quotes)</t>
+          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Replace the 5-minute batch refresh with sub-second streaming quotes during market hours so charts + price ladder + Trade Plan PnL update in real time.</t>
+          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Use the Schwab websocket feed (already in the paid stack — no new license per CLAUDE.md) into a local pub/sub buffer; kairos sub-tabs subscribe via SSE/WebSocket from server.py; cache TTL pinned at 1s during RTH.</t>
+          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>MODE-4</t>
+          <t>PARITY-PAPER-TRADING-RT</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -998,22 +998,22 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Execution / Paper / Platform Parity</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward validation of Phase-3 per-mode pillar weights</t>
+          <t>Real-Time Paper Trading</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>MODE-3 shipped intuition-based pillar weights without backtest evidence (principle 7 override). Need walk-forward validation that the per-mode weights don't degrade vs the single-set baseline.</t>
+          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>scripts/validate_per_mode_weights.py: runs baseline backtest + 3 mode-weighted backtests (252d, min_score=50), compares WR/PF/maxDD/Sharpe per mode. Revert criterion: any mode ≤1.0× PF or ≤-5pp WR vs baseline → flip per_mode_pillar_reweight._enabled to false. See docs/per_mode_decisions_roadmap.md Phase 3.</t>
+          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
     </row>
-    <row r="9" ht="75" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>PARITY-PAPER-TRADING-RT</t>
+          <t>REGIME-CONDITIONAL-MODELS</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1044,22 +1044,22 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Execution / Paper / Platform Parity</t>
+          <t>ML / Accuracy</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Real-Time Paper Trading</t>
+          <t>Regime-conditional ML models (principle 5)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Execute simulated trades against live market prices via the Alpaca paper account; track fills, slippage and PnL in real time so paper validation mirrors what live trading would look like.</t>
+          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to route signals through the Alpaca paper REST + websocket API; webhook fills back into cache/portfolio.json; expose a 'Paper Trade' toggle on the Trade Plan card. Partially built (executor.py --submit), needs always-on wrapper.</t>
+          <t>ml/train.py regime split</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>REGIME-CONDITIONAL-MODELS</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1090,27 +1090,39 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ML / Accuracy</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional ML models (principle 5)</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>train separate direction models per regime instead of one spanning all; #1 accuracy lever</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>ml/train.py regime split</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2 min</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Win: cleaner repo.</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Calendar reminder for 2026-05-16.</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1118,15 +1130,19 @@
       </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>SCHWAB-REAUTH-PENDING</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1136,39 +1152,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Ops / Schwab (operational)</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Schwab re-auth to unlock option Greeks</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Win: cleaner repo.</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Calendar reminder for 2026-05-16.</t>
-        </is>
-      </c>
+          <t>user action: schwab_auth.py oauth</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1176,11 +1180,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
+      <c r="N11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>SCHWAB-REAUTH-PENDING</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1198,27 +1198,39 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Ops / Schwab (operational)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Schwab re-auth to unlock option Greeks</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>refresh token expired (invalid_grant, 7-day). Run python3 schwab_auth.py oauth -&gt; real option premiums/Greeks flow into the Options calc (currently honest BS-model fallback).</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>user action: schwab_auth.py oauth</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: exploratory research, not config-tuning.</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+        </is>
+      </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1226,15 +1238,19 @@
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="165" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1244,37 +1260,37 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1286,17 +1302,17 @@
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="165" customHeight="1">
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>TEST-MAE-MFE</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1306,39 +1322,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Testing / Validation (Tier 1)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
+          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
+          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
-        </is>
-      </c>
+          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1346,11 +1350,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
-        </is>
-      </c>
+      <c r="N14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="2" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>TEST-MAE-MFE</t>
+          <t>TEST-MC-BOOTSTRAP</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>MAE / MFE Analyzer — tune stops + targets from data</t>
+          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Maximum Adverse Excursion vs Maximum Favorable Excursion analyzer. signal_log.json already tracks mae_pct + mfe_pct for closed trades. Output: 'Stops triggered at -5% on winners that later hit +20% → stops too tight' or 'Trades exited at +6% target left avg +12% on table → targets too conservative'. Directly improves trade-plan math.</t>
+          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log.json closed entries; scatter-plot mae vs realized PnL + mfe vs realized PnL; quantile bins (10/25/50/75/90); render as a new Testing tab card. Effort ~30min — data already there.</t>
+          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>TEST-MC-BOOTSTRAP</t>
+          <t>TEST-PERMUTATION</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Monte Carlo Bootstrap — confidence intervals on Sharpe/PF/WR</t>
+          <t>Permutation Test — is the edge REAL or coin flip?</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Randomly resample closed trades 10,000x to build distributions over each metric. Wilson LB only covers WR; this covers Sharpe, Sortino, PF, max-DD, hit-rate, payoff ratio. Output: 'Sharpe 1.42, 95% CI [0.88, 1.94]' — you would know whether 1.42 is robust or noise. Standard hedge-fund metric, supports principle #1 (statistical rigor).</t>
+          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Numpy bootstrap on signal_log trade PnL array, k=10000 resamples; compute distributions over each metric; render percentile bands. Effort 1-2hr.</t>
+          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>TEST-PERMUTATION</t>
+          <t>TEST-REGIME-COND</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Permutation Test — is the edge REAL or coin flip?</t>
+          <t>Regime-Conditional Performance — where does it work?</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Randomly shuffle BUY/SELL/AVOID labels on historical signals 1000x, recompute strategy returns. If real returns are not significantly better than scrambled returns, there is no edge. Direct test of principle #4 (adversarial mindset / falsification). Output: 'Real strategy: +18.7%. Random labels (1000 sims): +0.2% +/- 4.1%. p-value: 0.0001'.</t>
+          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Shuffle decision-column of signal_log 1000x; recompute portfolio return per shuffle; rank real return vs null distribution; report p-value. Effort ~1hr.</t>
+          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
@@ -1490,13 +1490,13 @@
       <c r="M17" s="3" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
     </row>
-    <row r="18" ht="90" customHeight="1">
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>TEST-REGIME-COND</t>
+          <t>REGIME-ACCURACY-TEST</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1506,22 +1506,22 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 1)</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Regime-Conditional Performance — where does it work?</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Partition closed trades by regime (risk_on_trending / choppy / risk_off / panic) and compute WR / PF / Sharpe per regime. Per principle #5 (regime conditioning over averages). Example output: 'Trend Continuation WR: 41% overall · 62% in risk_on_trending · 18% in choppy'. Tells you which sleeves to size up/down per regime.</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Group signal_log entries by regime_at_signal (already logged); compute Wilson LB on WR + bootstrapped PF/Sharpe per regime; output a (setup x regime) heatmap. Effort ~1hr.</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -1536,38 +1536,38 @@
       <c r="M18" s="3" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>PARITY-BACKTEST-UI</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>Backtesting / Platform Parity</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>In-app Backtesting UI</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>PARITY-BACKTEST-UI</t>
+          <t>BUG-MISSING-D1S</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1598,22 +1598,22 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Backtesting / Platform Parity</t>
+          <t>Bugs / Audit Ledger</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>In-app Backtesting UI</t>
+          <t>4 missing D1s for May 15 (out of 87)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Expose backtest.py + walk_forward_v2.py inside the kairos UI — a user picks a strategy/date range/universe and runs it without dropping to the terminal.</t>
+          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Backtest' workspace in the kairos sidebar; wire a form to a /v2/backtest endpoint that shells out to backtest.py and streams stdout via SSE; render Sharpe / PF / Wilson-LB / equity curve when the run completes.</t>
+          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>BUG-MISSING-D1S</t>
+          <t>PARITY-CHANNEL-BAR</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Bugs / Audit Ledger</t>
+          <t>Chart Indicators / Platform Parity</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>4 missing D1s for May 15 (out of 87)</t>
+          <t>Channel Bar overlay</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>4 of 87 May-15 picks have null D1 (next-day close). Probably thin EODHD coverage on small-caps — acceptable noise band but worth confirming.</t>
+          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Identify the 4 tickers; check EODHD eod() response for each on 2026-05-16; if EODHD returned null, document as known-limitation; if EODHD returned a value, fix the ingest. Effort ~20min.</t>
+          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CHANNEL-BAR</t>
+          <t>PARITY-RBI-GBI-WINDOW</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Channel Bar overlay</t>
+          <t>RBI/GBI Window (regime bias bands)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Donchian / Keltner / Bollinger envelope overlay on the chart — top + bottom band with mid-line.</t>
+          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Compute channels via pandas-ta in feature_extractor.py (or live in chart.js using bar data); render as semi-transparent band; toggle in the Chart sub-tab control bar.</t>
+          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1720,13 +1720,13 @@
       <c r="M22" s="3" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>PARITY-RBI-GBI-WINDOW</t>
+          <t>CLEAN-HOT-SECTORS-DEAD</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Chart Indicators / Platform Parity</t>
+          <t>Code Cleanup</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>RBI/GBI Window (regime bias bands)</t>
+          <t>panelHotSectors() dead-code in kairos.html</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Color-coded vertical bands on the chart timeline showing risk-on (green/GBI) vs risk-off (red/RBI) regime windows so the user can see at-a-glance whether prior price action happened in a hostile or friendly regime.</t>
+          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Read cache/regime_history.json and draw vertical color bands at each regime transition on the chart canvas; tooltip explains the regime classification (4-regime model: risk_on_trending / risk_on_choppy / risk_off_trending / panic).</t>
+          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-HOT-SECTORS-DEAD</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -1782,27 +1782,39 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>panelHotSectors() dead-code in kairos.html</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Hot Sectors panel was removed from the Signal Scanner grid but the panelHotSectors() function is still defined in kairos.html — dead code.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>grep for panelHotSectors callers; delete function + any unused helpers; verify no console errors. Effort ~2min.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Win: -X lines.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1810,15 +1822,19 @@
       </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+      <c r="N24" s="8" t="inlineStr">
+        <is>
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -1828,39 +1844,27 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Data / Calendars (future)</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>earnings_calendar_pit — point-in-time integrity</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Win: -X lines.</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Couples with OPS-1.</t>
-        </is>
-      </c>
+          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1868,19 +1872,15 @@
       </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+      <c r="N25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-EARNINGS-CAL-PIT</t>
+          <t>DATA-FUTURE-ECONOMIC-CAL</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>earnings_calendar_pit — point-in-time integrity</t>
+          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Earnings calendar with point-in-time integrity (what was expected when). Needed for clean PEAD backtest replay; today's calendar uses the most-recent snapshot only, which leaks future revisions into prior dates.</t>
+          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Snapshot the EODHD earnings calendar daily into a versioned earnings_calendar_history table; join on (ticker, report_date, snapshot_date) for PIT correctness in PEAD backtests.</t>
+          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-ECONOMIC-CAL</t>
+          <t>DATA-FUTURE-FDA-CAL</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>economic_calendar — CPI/PCE/NFP/FOMC dates</t>
+          <t>fda_calendar — PDUFA / AdCom dates</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Macro event calendar with consensus expectations. No source wired today; the pre-FOMC sleeve uses hard-coded FOMC dates and there is no CPI/PCE/NFP awareness.</t>
+          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Investing.com calendar scrape OR Trading Economics free tier; daily refresh; write to economic_calendar; feed pre-FOMC sleeve + risk_off blackout windows.</t>
+          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-FDA-CAL</t>
+          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -1982,22 +1982,22 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Data / Calendars (future)</t>
+          <t>Data / Corporate Actions (empty by sample)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>fda_calendar — PDUFA / AdCom dates</t>
+          <t>splits_calendar — 0 splits in current universe sample</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>FDA decision calendar (PDUFA dates, Advisory Committee meetings) for biotech catalyst tracking.</t>
+          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>FDA public calendar scrape + BiopharmCatalyst free RSS; write to fda_calendar; surface as catalyst tier in any biotech sleeve.</t>
+          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-SPLITS-CALENDAR</t>
+          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2028,22 +2028,22 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Data / Corporate Actions (empty by sample)</t>
+          <t>Data / ML (empty by design)</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>splits_calendar — 0 splits in current universe sample</t>
+          <t>model_calibration — waiting on realization</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>corporate_actions table populates from EODHD but the current universe sample (449 tickers) had 0 splits in the recent window. Calendar reads empty.</t>
+          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Expand corporate-actions polling universe to S&amp;P 500 + Russell 1000 (universe list already available); 1-line change in the populator script.</t>
+          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-MODEL-CALIBRATION</t>
+          <t>DATA-EMPTY-VAR-BREACHES</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Data / ML (empty by design)</t>
+          <t>Data / Risk (empty by design)</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>model_calibration — waiting on realization</t>
+          <t>var_breaches — waiting on snapshots + drawdown</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Calibration metrics table has no rows because the 5-20 day prediction horizons have not elapsed yet (today's predictions realize over 1-4 weeks).</t>
+          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively as time passes. Re-check after 2026-06-15 (30d post-shipping).</t>
+          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -2104,13 +2104,13 @@
       <c r="M30" s="3" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-VAR-BREACHES</t>
+          <t>DATA-FUTURE-INSIDER-EDGAR</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Data / Risk (empty by design)</t>
+          <t>Data / SEC EDGAR (future)</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>var_breaches — waiting on snapshots + drawdown</t>
+          <t>insider_transactions via Form 4 XBRL</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>VaR breach log empty because (1) daily portfolio_risk snapshots are still ramping up and (2) no real drawdown day has happened to trigger a breach.</t>
+          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>No code action; populates passively. Re-check after first portfolio drawdown &gt;2% or after 60 daily snapshots.</t>
+          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -2150,13 +2150,13 @@
       <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSIDER-EDGAR</t>
+          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>insider_transactions via Form 4 XBRL</t>
+          <t>institutional_holdings via 13F XBRL</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker insider buy/sell stream sourced direct from SEC Form 4 filings. Today sourced indirectly via Finviz Elite bulk; direct EDGAR is point-in-time accurate and free.</t>
+          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Build Form 4 XBRL parser; daily ingest from efts.sec.gov; write to insider_transactions table; reconcile against Finviz bulk for cross-check.</t>
+          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-INSTITUTIONAL-EDGAR</t>
+          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future)</t>
+          <t>Data / SEC EDGAR (future, alt for broken)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>institutional_holdings via 13F XBRL</t>
+          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Per-ticker institutional ownership tracking (Form 13F, quarterly). Useful for the Smart Money pillar; today only Finviz inst_own_pct snapshot.</t>
+          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>13F XBRL parser; quarterly ingest from EDGAR; write to institutional_holdings table with the 45-day reporting lag accounted for in any backtest joins.</t>
+          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-CONGRESSIONAL-EDGAR</t>
+          <t>SUPABASE-SYNC-VERIFY</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future, alt for broken)</t>
+          <t>Data / Supabase</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>congressional_trades via EDGAR / House Clerk (alt source)</t>
+          <t>Verify supabase_analysis_sync actually writes</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Alternate sourcing for congressional trades after Senate Stock Watcher death (see DATA-BROKEN-CONGRESSIONAL-TRADES). Direct from House Clerk + Senate eFD.</t>
+          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Scrape House STOCK Act PTR PDFs (House Clerk site); Senate eFD JSON; merge into normalized congressional_trades table.</t>
+          <t>supabase_analysis_sync.py</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
@@ -2288,13 +2288,13 @@
       <c r="M34" s="3" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SUPABASE-SYNC-VERIFY</t>
+          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -2304,22 +2304,22 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Data / Supabase</t>
+          <t>Data / Telemetry (deferred for safety)</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Verify supabase_analysis_sync actually writes</t>
+          <t>8 empty slots — production-engine touches deferred</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>confirm sync_scan writes (psycopg2 raw SQL not .table API); not silent no-op</t>
+          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>supabase_analysis_sync.py</t>
+          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>DATA-EMPTY-PROD-ENGINE-DEFERRED</t>
+          <t>EODHD-WIRES-VALIDATE</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Data / Telemetry (deferred for safety)</t>
+          <t>Data Wiring (validate)</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>8 empty slots — production-engine touches deferred</t>
+          <t>Validate EODHD-side wires on quota reset</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>8 telemetry/data slots remain empty because populating them requires editing backtest.py / executor.py / signal_filter.py / analysis.py. Deliberately deferred to avoid risk to the live scan + exec paths.</t>
+          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Enumerate the 8 specifically and grade each one for in-place vs side-car instrumentation. Side-car (write to telemetry DB without changing decision flow) is preferred over hot-path edits.</t>
+          <t>Stocksmith.html /api/fundamentals consumers</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -2380,13 +2380,13 @@
       <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
     </row>
-    <row r="37" ht="60" customHeight="1">
+    <row r="37" ht="75" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>EODHD-WIRES-VALIDATE</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -2396,22 +2396,22 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring (validate)</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Validate EODHD-side wires on quota reset</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>DCF net-debt/FCF + per-name beta + Book Risk crowding are code-complete + fallback-safe but untested against live EODHD (quota was exhausted). Confirm real values flow after reset.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html /api/fundamentals consumers</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -2426,13 +2426,13 @@
       <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
     </row>
-    <row r="38" ht="75" customHeight="1">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
       <c r="M38" s="3" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
     </row>
-    <row r="39" ht="60" customHeight="1">
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
@@ -2488,22 +2488,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
@@ -2534,22 +2534,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -2564,13 +2564,13 @@
       <c r="M40" s="3" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
     </row>
-    <row r="41" ht="75" customHeight="1">
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
@@ -2610,13 +2610,13 @@
       <c r="M41" s="3" t="inlineStr"/>
       <c r="N41" s="8" t="inlineStr"/>
     </row>
-    <row r="42" ht="45" customHeight="1">
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
@@ -2631,17 +2631,17 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2718,22 +2718,22 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,22 +2764,22 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2794,13 +2794,13 @@
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
     </row>
-    <row r="46" ht="60" customHeight="1">
+    <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>SLACK-NEWSLETTER-MLALERT</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>infra/launchd + scripts/ml_alert_slack.py</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SLACK-NEWSLETTER-MLALERT</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2856,22 +2856,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Re-enable newsletter + add ML-predictions Slack alert</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>re-enable daily-newsletter from disabled/; build ml-alert Slack for top ML-edge/AI picks</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd + scripts/ml_alert_slack.py</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2902,22 +2902,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -2999,17 +2999,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3024,13 +3024,13 @@
       <c r="M50" s="3" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
     </row>
-    <row r="51" ht="45" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3040,22 +3040,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
       <c r="M51" s="3" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
     </row>
-    <row r="52" ht="60" customHeight="1">
+    <row r="52" ht="90" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3086,22 +3086,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3116,13 +3116,13 @@
       <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
     </row>
-    <row r="53" ht="90" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3132,22 +3132,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3178,22 +3178,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3254,13 +3254,13 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
     </row>
-    <row r="56" ht="60" customHeight="1">
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3300,13 +3300,13 @@
       <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
     </row>
-    <row r="57" ht="45" customHeight="1">
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3459,17 +3459,17 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3500,22 +3500,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3530,13 +3530,13 @@
       <c r="M61" s="3" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
     </row>
-    <row r="62" ht="60" customHeight="1">
+    <row r="62" ht="45" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3551,17 +3551,17 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3576,13 +3576,13 @@
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
     </row>
-    <row r="63" ht="45" customHeight="1">
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3597,17 +3597,17 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3730,22 +3730,22 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3760,13 +3760,13 @@
       <c r="M66" s="3" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
     </row>
-    <row r="67" ht="60" customHeight="1">
+    <row r="67" ht="45" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3776,22 +3776,22 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3822,22 +3822,22 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3852,13 +3852,13 @@
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
     </row>
-    <row r="69" ht="45" customHeight="1">
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3914,22 +3914,22 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3960,22 +3960,22 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4036,13 +4036,13 @@
       <c r="M72" s="3" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
     </row>
-    <row r="73" ht="60" customHeight="1">
+    <row r="73" ht="75" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4052,35 +4052,51 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="5" t="inlineStr"/>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K73" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="3" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="75" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -4088,69 +4104,77 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="90" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -4160,37 +4184,29 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
@@ -4200,27 +4216,27 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="75" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4230,31 +4246,27 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J76" s="5" t="inlineStr"/>
       <c r="K76" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4267,22 +4279,18 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N76" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77" ht="45" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -4292,27 +4300,39 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4325,18 +4345,22 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N77" s="8" t="inlineStr"/>
-    </row>
-    <row r="78" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="75" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -4346,39 +4370,27 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4386,27 +4398,23 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N78" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79" ht="90" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -4416,27 +4424,39 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4444,23 +4464,27 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N79" s="8" t="inlineStr"/>
-    </row>
-    <row r="80" ht="90" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="105" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4470,22 +4494,22 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4495,12 +4519,12 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
@@ -4510,27 +4534,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="45" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -4540,37 +4564,37 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -4580,27 +4604,27 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="120" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4610,39 +4634,27 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
       <c r="K82" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4655,22 +4667,18 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N82" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N82" s="8" t="inlineStr"/>
+    </row>
+    <row r="83" ht="60" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4680,27 +4688,39 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K83" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4708,23 +4728,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N83" s="8" t="inlineStr"/>
-    </row>
-    <row r="84" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4739,32 +4763,32 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -4784,7 +4808,7 @@
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4818,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4809,17 +4833,17 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4829,12 +4853,12 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K85" s="12" t="inlineStr">
@@ -4854,17 +4878,17 @@
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4879,32 +4903,32 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K86" s="12" t="inlineStr">
@@ -4914,27 +4938,27 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="180" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4949,32 +4973,32 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K87" s="12" t="inlineStr">
@@ -4989,22 +5013,22 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -5019,32 +5043,32 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K88" s="12" t="inlineStr">
@@ -5059,22 +5083,22 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="90" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -5084,37 +5108,37 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
@@ -5124,27 +5148,27 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N89" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5154,22 +5178,22 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5179,12 +5203,12 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
@@ -5199,12 +5223,12 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5238,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5229,32 +5253,32 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K91" s="12" t="inlineStr">
@@ -5269,22 +5293,22 @@
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="105" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5294,37 +5318,29 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K92" s="12" t="inlineStr">
@@ -5334,27 +5350,27 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5364,29 +5380,37 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K93" s="12" t="inlineStr">
@@ -5396,27 +5420,27 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N93" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="90" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5426,37 +5450,37 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K94" s="12" t="inlineStr">
@@ -5466,27 +5490,27 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N94" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="75" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5496,39 +5520,27 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="5" t="inlineStr"/>
       <c r="K95" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5541,22 +5553,18 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N95" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N95" s="8" t="inlineStr"/>
+    </row>
+    <row r="96" ht="45" customHeight="1">
       <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5566,27 +5574,39 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr"/>
-      <c r="J96" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5599,18 +5619,22 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5620,37 +5644,37 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K97" s="12" t="inlineStr">
@@ -5660,17 +5684,17 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N97" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5704,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -5695,17 +5719,17 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5715,12 +5739,12 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
@@ -5735,12 +5759,12 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N98" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5774,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>STRATEGY-TUNE-20260519</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5760,39 +5784,27 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy Tuning</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>5 data-backed fixes from 986-trade backtest analysis</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>decision_engine.py + config.json</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="5" t="inlineStr"/>
       <c r="K99" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5800,27 +5812,23 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N99" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="60" customHeight="1">
+          <t>29578a5fb</t>
+        </is>
+      </c>
+      <c r="N99" s="8" t="inlineStr"/>
+    </row>
+    <row r="100" ht="75" customHeight="1">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>STRATEGY-TUNE-20260519</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5830,22 +5838,22 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Strategy Tuning</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>5 data-backed fixes from 986-trade backtest analysis</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>decision_engine.py + config.json</t>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
@@ -5858,23 +5866,23 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>29578a5fb</t>
+          <t>87336f2de</t>
         </is>
       </c>
       <c r="N100" s="8" t="inlineStr"/>
     </row>
-    <row r="101" ht="75" customHeight="1">
+    <row r="101" ht="45" customHeight="1">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>STOCKSMITH-MODE-CASCADE</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5884,22 +5892,22 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>V2 Dashboard / Detail</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr"/>
@@ -5912,12 +5920,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>eb83a151d</t>
         </is>
       </c>
       <c r="N101" s="8" t="inlineStr"/>
@@ -5928,7 +5936,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-MODE-CASCADE</t>
+          <t>STOCKSMITH-AI-CHART</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5938,22 +5946,22 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Detail</t>
+          <t>V2 Dashboard / ML Predictions</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
+          <t>AI Price-Projection Chart (§1)</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
+          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
+          <t>Stocksmith.html AIProjectionChart</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
@@ -5971,7 +5979,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>eb83a151d</t>
+          <t>a5dcb06c9</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr"/>
@@ -5982,7 +5990,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-AI-CHART</t>
+          <t>STOCKSMITH-OPTIONS-CALC</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5992,22 +6000,22 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / ML Predictions</t>
+          <t>V2 Dashboard / Options</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>AI Price-Projection Chart (§1)</t>
+          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
+          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AIProjectionChart</t>
+          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr"/>
@@ -6025,7 +6033,7 @@
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>a5dcb06c9</t>
+          <t>932cef7fe</t>
         </is>
       </c>
       <c r="N103" s="8" t="inlineStr"/>
@@ -6036,32 +6044,32 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-OPTIONS-CALC</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PICK-FORENSICS</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Options</t>
+          <t>Audit / Attribution</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
+          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
+          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
+          <t>scripts/pick_forensics.py + dashboard tab</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr"/>
@@ -6074,12 +6082,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>932cef7fe</t>
+          <t>5e6375889</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr"/>
@@ -14324,13 +14332,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>54</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -14362,13 +14370,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>59</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-31.xlsx
+++ b/cache/open_items_2026-05-31.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N240"/>
+  <dimension ref="A1:N241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12020,13 +12020,13 @@
       </c>
       <c r="N202" s="8" t="inlineStr"/>
     </row>
-    <row r="203" ht="75" customHeight="1">
+    <row r="203" ht="45" customHeight="1">
       <c r="A203" s="2" t="n">
         <v>202</v>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>FORENSICS-WEEKLY-SLACK</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -12036,39 +12036,27 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Notifications / Audit</t>
         </is>
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Weekly pick-forensics Slack digest</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Sun 17:30 — 14d verdict-truth + per-sleeve EXTENDED/MISSED bleeding monitor to Slack</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I203" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J203" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>com.swingtrade.forensics-weekly + pick_forensics --slack</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr"/>
+      <c r="I203" s="5" t="inlineStr"/>
+      <c r="J203" s="5" t="inlineStr"/>
       <c r="K203" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12076,27 +12064,23 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N203" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N203" s="8" t="inlineStr"/>
+    </row>
+    <row r="204" ht="75" customHeight="1">
       <c r="A204" s="2" t="n">
         <v>203</v>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -12106,37 +12090,37 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J204" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K204" s="12" t="inlineStr">
@@ -12146,17 +12130,17 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N204" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12150,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
@@ -12181,32 +12165,32 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J205" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K205" s="12" t="inlineStr">
@@ -12226,7 +12210,7 @@
       </c>
       <c r="N205" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12220,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
@@ -12251,32 +12235,32 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J206" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K206" s="12" t="inlineStr">
@@ -12296,7 +12280,7 @@
       </c>
       <c r="N206" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12290,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
@@ -12321,32 +12305,32 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J207" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K207" s="12" t="inlineStr">
@@ -12356,27 +12340,27 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N207" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="45" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="60" customHeight="1">
       <c r="A208" s="2" t="n">
         <v>207</v>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>SCAN-FAILURE-ALERT</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -12386,27 +12370,39 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Ops / Alerts</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Scan-failure + EODHD-quota Slack alert</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>swing_trade.py exit hook</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="inlineStr"/>
-      <c r="I208" s="5" t="inlineStr"/>
-      <c r="J208" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
       <c r="K208" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12414,15 +12410,19 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>0dc7675ee</t>
-        </is>
-      </c>
-      <c r="N208" s="8" t="inlineStr"/>
+          <t>2b7d2f40f</t>
+        </is>
+      </c>
+      <c r="N208" s="8" t="inlineStr">
+        <is>
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="45" customHeight="1">
       <c r="A209" s="2" t="n">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
+          <t>SCAN-FAILURE-ALERT</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
@@ -12440,22 +12440,22 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Alerts</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot: load or retire</t>
+          <t>Scan-failure + EODHD-quota Slack alert</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
+          <t>failed scan / 402 quota is silent today; 1-line health alert on scan exit</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd</t>
+          <t>swing_trade.py exit hook</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12478,13 +12478,13 @@
       </c>
       <c r="N209" s="8" t="inlineStr"/>
     </row>
-    <row r="210" ht="150" customHeight="1">
+    <row r="210" ht="45" customHeight="1">
       <c r="A210" s="2" t="n">
         <v>209</v>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>MOMENTUM-SNAPSHOT-DECIDE</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12494,31 +12494,27 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Decide momentum-snapshot: load or retire</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>valid plist, not loaded; PARSE-ERR on lint earlier</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>infra/launchd</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
       <c r="I210" s="5" t="inlineStr"/>
-      <c r="J210" s="5" t="inlineStr">
-        <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
+      <c r="J210" s="5" t="inlineStr"/>
       <c r="K210" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12526,27 +12522,23 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
-        </is>
-      </c>
-      <c r="N210" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="45" customHeight="1">
+          <t>0dc7675ee</t>
+        </is>
+      </c>
+      <c r="N210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211" ht="150" customHeight="1">
       <c r="A211" s="2" t="n">
         <v>210</v>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-1</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12556,27 +12548,31 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Sharpe Roadmap</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>Sharpe gate in momentum detector</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
       <c r="I211" s="5" t="inlineStr"/>
-      <c r="J211" s="5" t="inlineStr"/>
+      <c r="J211" s="5" t="inlineStr">
+        <is>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
       <c r="K211" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -12584,15 +12580,19 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>dbbd6b5f6</t>
-        </is>
-      </c>
-      <c r="N211" s="8" t="inlineStr"/>
+          <t>cf30df858</t>
+        </is>
+      </c>
+      <c r="N211" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="45" customHeight="1">
       <c r="A212" s="2" t="n">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-10</t>
+          <t>SHARPE-1</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12615,17 +12615,17 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>Sharpe alerts for watchlist</t>
+          <t>Sharpe gate in momentum detector</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Wire 126d Sharpe threshold (≥1.5) into _detect_momentum_continuation</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
+          <t>Computed inline in analyze_ticker via lib.sharpe_utils.sharpe_annualized; passed to detector as kwarg</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-11</t>
+          <t>SHARPE-10</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12669,17 +12669,17 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>Per-trade Sharpe attribution</t>
+          <t>Sharpe alerts for watchlist</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
+          <t>scripts/sharpe_alert.py — tracks state across runs, posts to SLACK_WEBHOOK_URL</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-12</t>
+          <t>SHARPE-11</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12723,17 +12723,17 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>Sharpe consistency check</t>
+          <t>Per-trade Sharpe attribution</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Decompose portfolio Sharpe by ticker / setup / regime contribution</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
+          <t>Built into scripts/sharpe_kpi.py — top contributors / detractors + setup + regime contribution tables</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12762,7 +12762,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-2</t>
+          <t>SHARPE-12</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12777,17 +12777,17 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>Sharpe column in v2 dashboard</t>
+          <t>Sharpe consistency check</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Surface 126d Sharpe per ticker as sortable column</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
+          <t>lib.sharpe_utils.rolling_sharpe + consistency_score; surfaced on per-ticker result dict</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-3</t>
+          <t>SHARPE-2</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12831,17 +12831,17 @@
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>Per-stock Sharpe by regime</t>
+          <t>Sharpe column in v2 dashboard</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Decompose per-stock Sharpe by historical regime tags</t>
+          <t>Surface 126d Sharpe per ticker as sortable column</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
+          <t>Added sharpe_126d / sortino_126d / sharpe_consistency to compact_row in build_data.py</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12870,7 +12870,7 @@
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-4</t>
+          <t>SHARPE-3</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
+          <t>Per-stock Sharpe by regime</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
+          <t>Decompose per-stock Sharpe by historical regime tags</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
+          <t>scripts/sharpe_per_regime.py — segments OHLCV by regime, computes per-bucket Sharpe</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-5</t>
+          <t>SHARPE-4</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12939,17 +12939,17 @@
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-weighted position sizing</t>
+          <t>Edge-erosion radar (per-setup Sharpe trend)</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Per-setup Sharpe across rolling windows w/ HTML viz</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_setup_trend.py — emits trend table + dark-themed HTML chart per setup</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-6</t>
+          <t>SHARPE-5</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12993,17 +12993,17 @@
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Portfolio Sharpe KPI vs target</t>
+          <t>Sharpe-weighted position sizing</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Annualized Sharpe target tracking + gap report</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
+          <t>kelly_position_size new sharpe_126d kwarg + portfolio.sharpe_size_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-7</t>
+          <t>SHARPE-6</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
@@ -13047,17 +13047,17 @@
       </c>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>Sharpe-based stop sizing</t>
+          <t>Portfolio Sharpe KPI vs target</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Annualized Sharpe target tracking + gap report</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
+          <t>scripts/sharpe_kpi.py — reports actual vs target/floor, exits 2 on below-floor for cron alerts</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-8</t>
+          <t>SHARPE-7</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -13101,17 +13101,17 @@
       </c>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>Sortino computation alongside Sharpe</t>
+          <t>Sharpe-based stop sizing</t>
         </is>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Downside-only vol denominator added everywhere</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
+          <t>compute_trade_plan reads runtime sharpe; portfolio.sharpe_stop_tilt config block (default OFF)</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr"/>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>SHARPE-9</t>
+          <t>SHARPE-8</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
@@ -13155,17 +13155,17 @@
       </c>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>SPY-Sharpe regime cross-validation</t>
+          <t>Sortino computation alongside Sharpe</t>
         </is>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Implements item from Sharpe roadmap brainstorm</t>
+          <t>Downside-only vol denominator added everywhere</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+          <t>lib.sharpe_utils.sortino_annualized + per_trade_sortino; surfaced on result dict</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr"/>
@@ -13188,13 +13188,13 @@
       </c>
       <c r="N222" s="8" t="inlineStr"/>
     </row>
-    <row r="223" ht="120" customHeight="1">
+    <row r="223" ht="45" customHeight="1">
       <c r="A223" s="2" t="n">
         <v>222</v>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>SHARPE-9</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
@@ -13204,39 +13204,27 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Sharpe Roadmap</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>SPY-Sharpe regime cross-validation</t>
         </is>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Implements item from Sharpe roadmap brainstorm</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I223" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
-      <c r="J223" s="5" t="inlineStr">
-        <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
-        </is>
-      </c>
+          <t>data_fetcher.get_market_regime now includes spy_sharpe payload</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr"/>
+      <c r="I223" s="5" t="inlineStr"/>
+      <c r="J223" s="5" t="inlineStr"/>
       <c r="K223" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13244,27 +13232,23 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N223" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="75" customHeight="1">
+          <t>dbbd6b5f6</t>
+        </is>
+      </c>
+      <c r="N223" s="8" t="inlineStr"/>
+    </row>
+    <row r="224" ht="120" customHeight="1">
       <c r="A224" s="2" t="n">
         <v>223</v>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-Q-AB</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
@@ -13274,27 +13258,39 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Gates</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entry_quality A/B</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
-        </is>
-      </c>
-      <c r="H224" s="2" t="inlineStr"/>
-      <c r="I224" s="5" t="inlineStr"/>
-      <c r="J224" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="inlineStr">
+        <is>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+        </is>
+      </c>
       <c r="K224" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13302,23 +13298,27 @@
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>07c3af6a3</t>
-        </is>
-      </c>
-      <c r="N224" s="8" t="inlineStr"/>
-    </row>
-    <row r="225" ht="120" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N224" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="75" customHeight="1">
       <c r="A225" s="2" t="n">
         <v>224</v>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>UI-STRAT-1</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
@@ -13328,22 +13328,22 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Strategy Lab</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -13356,23 +13356,23 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>93ec11842</t>
+          <t>07c3af6a3</t>
         </is>
       </c>
       <c r="N225" s="8" t="inlineStr"/>
     </row>
-    <row r="226" ht="105" customHeight="1">
+    <row r="226" ht="120" customHeight="1">
       <c r="A226" s="2" t="n">
         <v>225</v>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>UI-STRAT-1</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
@@ -13382,31 +13382,27 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy Lab</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>13-section HF cockpit rebuild + live setup_stats wiring</t>
         </is>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Old Strategy Lab was 4-section table with fake numbers and 3x3 correlation. Didn't match 20yr HF analyst standard (no capital allocation cascade, no Wilson CI on PF, no edge-erosion radar, no BT vs Live divergence, no auto-quarantine surface).</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+          <t>Rebuilt renderStrategies in kairos.html with 13 sections: portfolio cockpit, setup-family perf (LIVE from setup_stats.json with Wilson bars + PF haircut), edge erosion radar, BT vs Live divergence (surfaces PEAD canary BT 2.04 vs live 0.88), phase promotion ledger, regime×sleeve grid 8x4, correlation 8x8 + eigenvalue λ₁, sleeve interaction overlap, recent picks roster, auto-quarantine surface, mechanism+falsifier, playbook, pre-mortem. async _stratLabPatch() fetches live data.</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
       <c r="I226" s="5" t="inlineStr"/>
-      <c r="J226" s="5" t="inlineStr">
-        <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
+      <c r="J226" s="5" t="inlineStr"/>
       <c r="K226" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13414,27 +13410,23 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N226" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="135" customHeight="1">
+          <t>93ec11842</t>
+        </is>
+      </c>
+      <c r="N226" s="8" t="inlineStr"/>
+    </row>
+    <row r="227" ht="105" customHeight="1">
       <c r="A227" s="2" t="n">
         <v>226</v>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
@@ -13444,37 +13436,29 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I227" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr"/>
+      <c r="I227" s="5" t="inlineStr"/>
       <c r="J227" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K227" s="12" t="inlineStr">
@@ -13484,27 +13468,27 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N227" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="135" customHeight="1">
       <c r="A228" s="2" t="n">
         <v>227</v>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-BOOK-RISK</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
@@ -13514,27 +13498,39 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Risk</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
         <is>
-          <t>Book Risk surface + per-lens analytics (§6)</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="5" t="inlineStr"/>
-      <c r="J228" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
+      <c r="J228" s="5" t="inlineStr">
+        <is>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
       <c r="K228" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13542,23 +13538,27 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>50cace567</t>
-        </is>
-      </c>
-      <c r="N228" s="8" t="inlineStr"/>
-    </row>
-    <row r="229" ht="120" customHeight="1">
+          <t>42c36ef91</t>
+        </is>
+      </c>
+      <c r="N228" s="8" t="inlineStr">
+        <is>
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="45" customHeight="1">
       <c r="A229" s="2" t="n">
         <v>228</v>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>STOCKSMITH-BOOK-RISK</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
@@ -13568,31 +13568,27 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>V2 Dashboard / Risk</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Book Risk surface + per-lens analytics (§6)</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Book Risk (exposure/Greeks/optimizer/attribution/crowding/hedge) + VaR mode-aware + DCF grid + Earnings whisper; honest dashes</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Stocksmith.html BookRiskPanel + InvDcfSensitivity + EoWhisperRevisions</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="5" t="inlineStr"/>
-      <c r="J229" s="5" t="inlineStr">
-        <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
+      <c r="J229" s="5" t="inlineStr"/>
       <c r="K229" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13600,27 +13596,23 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N229" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="60" customHeight="1">
+          <t>50cace567</t>
+        </is>
+      </c>
+      <c r="N229" s="8" t="inlineStr"/>
+    </row>
+    <row r="230" ht="120" customHeight="1">
       <c r="A230" s="2" t="n">
         <v>229</v>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>MOMENTUM-TAB</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
@@ -13630,27 +13622,31 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Momentum</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
         <is>
-          <t>New 🚀 Momentum workspace tab</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="5" t="inlineStr"/>
-      <c r="J230" s="5" t="inlineStr"/>
+      <c r="J230" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K230" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13658,15 +13654,19 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N230" s="8" t="inlineStr"/>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N230" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="60" customHeight="1">
       <c r="A231" s="2" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SCANNER-QUICK-PANELS</t>
+          <t>MOMENTUM-TAB</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
@@ -13684,22 +13684,22 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Workspaces / Signal Scanner</t>
+          <t>Workspaces / Momentum</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
         <is>
-          <t>5 quick-glance panels above watchlist table</t>
+          <t>New 🚀 Momentum workspace tab</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
+          <t>Ranks scan universe by composite (raw_momentum_score×0.5 + sharpe_norm×0.25 + rs_rank×0.25). Filterable by setup family + grade A/B/C. Click row → detail. Sidebar count = Grade-A + composite≥80 tickers</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+          <t>kairos.html QuantMomentum IIFE + V3_WORKSPACES.momentum + dispatcher branch</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr"/>
@@ -13717,60 +13717,48 @@
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N231" s="8" t="inlineStr"/>
     </row>
-    <row r="232" ht="45" customHeight="1">
+    <row r="232" ht="60" customHeight="1">
       <c r="A232" s="2" t="n">
         <v>231</v>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C232" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>SCANNER-QUICK-PANELS</t>
+        </is>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Workspaces / Signal Scanner</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>5 quick-glance panels above watchlist table</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Top 5 AI Predictions · Fresh Entries · Top Momentum · Earnings This Week · Volume Surges. Each panel uses shared _qpCard + _qpFrame helpers. Click row → setDetailTicker (with ML cache fallback for R2000)</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H232" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
-      <c r="J232" s="5" t="inlineStr">
-        <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
+          <t>kairos.html QuantScanner.renderQuickPanels + panelXxx helpers + .qs-quick-* CSS</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr"/>
+      <c r="I232" s="5" t="inlineStr"/>
+      <c r="J232" s="5" t="inlineStr"/>
       <c r="K232" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13778,15 +13766,15 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M232" s="3" t="inlineStr"/>
-      <c r="N232" s="8" t="inlineStr">
-        <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>dfbe955fe</t>
+        </is>
+      </c>
+      <c r="N232" s="8" t="inlineStr"/>
     </row>
     <row r="233" ht="45" customHeight="1">
       <c r="A233" s="2" t="n">
@@ -13794,7 +13782,7 @@
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C233" s="13" t="inlineStr">
@@ -13809,32 +13797,32 @@
       </c>
       <c r="E233" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J233" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K233" s="12" t="inlineStr">
@@ -13850,7 +13838,7 @@
       <c r="M233" s="3" t="inlineStr"/>
       <c r="N233" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13848,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C234" s="13" t="inlineStr">
@@ -13870,35 +13858,39 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J234" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J234" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K234" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -13906,17 +13898,13 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M234" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M234" s="3" t="inlineStr"/>
       <c r="N234" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -13926,59 +13914,63 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C235" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C235" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J235" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K235" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L235" s="2" t="inlineStr"/>
-      <c r="M235" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J235" s="5" t="inlineStr"/>
+      <c r="K235" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N235" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13980,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
@@ -13998,37 +13990,37 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J236" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K236" s="14" t="inlineStr">
@@ -14050,109 +14042,109 @@
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C237" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J237" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K237" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K237" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="45" customHeight="1">
       <c r="A238" s="2" t="n">
         <v>237</v>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C238" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J238" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K238" s="15" t="inlineStr">
@@ -14160,147 +14152,209 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L238" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L238" s="2" t="inlineStr"/>
       <c r="M238" s="3" t="inlineStr"/>
       <c r="N238" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="195" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="75" customHeight="1">
       <c r="A239" s="2" t="n">
         <v>238</v>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>UI / Modularization</t>
+        </is>
+      </c>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>Pixel-diff regression baseline</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>After modularization, no automated visual-regression catch.</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I239" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J239" s="5" t="inlineStr">
+        <is>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K239" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr"/>
+      <c r="N239" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="195" customHeight="1">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
           <t>OB-CONFLUENCE-PROPOSAL-REJECTED</t>
         </is>
       </c>
-      <c r="C239" s="10" t="inlineStr">
+      <c r="C240" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D239" s="5" t="inlineStr">
+      <c r="D240" s="5" t="inlineStr">
         <is>
           <t>Signals / Cross-Check</t>
         </is>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>OB-confluence Wilson bump + OB-aware stop — proposals KILLED by backtest evidence</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
+      <c r="F240" s="5" t="inlineStr">
         <is>
           <t>User asked 2026-05-12 to ship #2 (Wilson-bump score factor for bullish OB confluence within 5% of entry) and #5 (OB-low as stop instead of 1.25xATR). Per Principle 1 / Principle 7, ran post-hoc validation: scripts/validate_ob_confluence.py retroactively tags every closed trade from existing portfolio_backtest outputs with SMC state at entry date, computes Wilson 95% LB per subset.
 RESULT (750-day backtest · n=384): Bull OB confluence within 5% of entry DECREASES Wilson LB by -8.6pp (14.6% vs baseline 23.1%). BOS-bullish boost: -3.4pp. SMC-bullish direction boost: -3.6pp. Per #5 simulation, 35 of 39 (90%) OB-low-as-stop would have loosened the stop; 25 of those still ended in losses (looser stops do not rescue broken setups, they extend exposure).
 Principle 4 fires: proposals FALSIFIED, killed permanently (not retuned). Doing the change without this validation would have introduced a 6-9pp Wilson-LB drag on every BUY signal.</t>
         </is>
       </c>
-      <c r="G239" s="5" t="inlineStr">
+      <c r="G240" s="5" t="inlineStr">
         <is>
           <t>Built scripts/validate_ob_confluence.py to retroactively run smart_money.score_smc() on the historical OHLCV at each trade's entry date, tag with OB-confluence + BOS + CHoCH flags, compute Wilson 95% LB per subset, and apply Principle 1 gates (n&gt;=30, lift&gt;=5pp). Cross-validated on 250d (n=142) and 750d (n=384) backtest outputs. Both agree: NO EDGE.</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Days of work avoided (would have shipped a degrading change).</t>
         </is>
       </c>
-      <c r="I239" s="5" t="inlineStr">
+      <c r="I240" s="5" t="inlineStr">
         <is>
           <t>Mechanism (Principle 2): institutional OBs are supposed to mark re-add zones for smart money. Falsification (Principle 4): if the data doesn't show OB-confluent trades winning more, the mechanism either doesn't exist for retail-accessible OB detection at daily resolution OR is already priced into our 5-pillar score. Either way: ship nothing. The proposals are dead. Win: prevented a 6-9pp Wilson-LB drag from being added to live scoring. Lost: nothing — we didn't change live scoring, no opportunity cost.</t>
         </is>
       </c>
-      <c r="J239" s="5" t="inlineStr">
+      <c r="J240" s="5" t="inlineStr">
         <is>
           <t>Validator script is reusable infrastructure. Re-run any time the SMC detection logic or score thresholds change. NOTE: baseline WR in 750d backtest is 27.3% (low) — the absolute level reflects backtest-window-specific market conditions; the SUBSET comparisons are valid regardless because they share the same baseline. Do not interpret 23.1% Wilson LB as a system-level edge — that's a separate question. This validation answers ONLY: does OB-confluence improve selection within whatever the system already does.</t>
         </is>
       </c>
-      <c r="K239" s="15" t="inlineStr">
+      <c r="K240" s="15" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L239" s="2" t="inlineStr">
+      <c r="L240" s="2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="M239" s="3" t="inlineStr"/>
-      <c r="N239" s="8" t="inlineStr">
-        <is>
-          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="90" customHeight="1">
-      <c r="A240" s="2" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C240" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="D240" s="5" t="inlineStr">
-        <is>
-          <t>Data / Universe</t>
-        </is>
-      </c>
-      <c r="E240" s="6" t="inlineStr">
-        <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
-        </is>
-      </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr">
-        <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
-        </is>
-      </c>
-      <c r="H240" s="2" t="inlineStr">
-        <is>
-          <t>$$ + 1 day</t>
-        </is>
-      </c>
-      <c r="I240" s="5" t="inlineStr">
-        <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
-        </is>
-      </c>
-      <c r="J240" s="5" t="inlineStr">
-        <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K240" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr"/>
       <c r="N240" s="8" t="inlineStr">
+        <is>
+          <t>python3 scripts/validate_ob_confluence.py --backtest cache/portfolio_backtest_750d_20260509_100501.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="90" customHeight="1">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C241" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I241" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J241" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K241" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr"/>
+      <c r="N241" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -14405,10 +14459,10 @@
         <v>70</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5">
@@ -14462,10 +14516,10 @@
         <v>86</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
